--- a/torre_de_control_CCR - Copy.xlsx
+++ b/torre_de_control_CCR - Copy.xlsx
@@ -8,24 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/alvarobo_iadb_org/Documents/Documents/GitHub/torre-control-ccr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46AD3122-4942-48F6-9B55-A6EFDDD341DD}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="13_ncr:1_{75047D51-A796-4CC0-AB19-45877F10B4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF2EAB07-5D96-4F5F-BD3B-B91100B57C3D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="documentos" sheetId="1" r:id="rId1"/>
     <sheet name="equipo" sheetId="2" r:id="rId2"/>
-    <sheet name="clausulas vencidas" sheetId="3" r:id="rId3"/>
-    <sheet name="clausulas 180 dias" sheetId="4" r:id="rId4"/>
-    <sheet name="productos criticos" sheetId="5" r:id="rId5"/>
-    <sheet name="PMR" sheetId="6" r:id="rId6"/>
-    <sheet name="datos_ops" sheetId="8" r:id="rId7"/>
-    <sheet name="change log" sheetId="7" r:id="rId8"/>
+    <sheet name="productos criticos" sheetId="5" r:id="rId3"/>
+    <sheet name="PMR" sheetId="6" r:id="rId4"/>
+    <sheet name="datos_ops" sheetId="8" r:id="rId5"/>
+    <sheet name="change log" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'clausulas 180 dias'!$B$4:$K$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">documentos!$A$3:$D$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'productos criticos'!$B$3:$G$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'productos criticos'!$B$3:$G$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="400">
   <si>
     <t>Documentos por Operación — Torre de Control CCR</t>
   </si>
@@ -563,139 +560,22 @@
     <t>Analista 6</t>
   </si>
   <si>
-    <t>Clause ID</t>
-  </si>
-  <si>
-    <t>Clause Number</t>
-  </si>
-  <si>
     <t>Programa</t>
   </si>
   <si>
-    <t>UDR</t>
-  </si>
-  <si>
-    <t>Status Cláusula</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Descripción de la cláusula</t>
-  </si>
-  <si>
-    <t>Fecha de vencimiento</t>
-  </si>
-  <si>
-    <t>Comentario</t>
-  </si>
-  <si>
     <t>4871/OC-CR</t>
   </si>
   <si>
-    <t>CID/CCR</t>
-  </si>
-  <si>
-    <t>TRACK</t>
-  </si>
-  <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t>Cláusula 4.08 - S1</t>
-  </si>
-  <si>
-    <t>Sectorial</t>
-  </si>
-  <si>
-    <t>Informe de Mantenimiento de obras y equipos</t>
-  </si>
-  <si>
-    <t>Cláusula 5.03</t>
-  </si>
-  <si>
-    <t>Datos Comparativos anuales de las matrices de resultados</t>
-  </si>
-  <si>
-    <t>4.02 (b)</t>
-  </si>
-  <si>
     <t>3072/CH-CR</t>
   </si>
   <si>
-    <t>Informe Anual de Mantenimiento</t>
-  </si>
-  <si>
     <t>3071/OC-CR</t>
   </si>
   <si>
-    <t>8.03</t>
-  </si>
-  <si>
     <t>4864/OC-CR</t>
   </si>
   <si>
-    <t>Informe Semestral de Progreso</t>
-  </si>
-  <si>
-    <t>Contract ID</t>
-  </si>
-  <si>
-    <t>LMS Number</t>
-  </si>
-  <si>
-    <t>Clause Status</t>
-  </si>
-  <si>
-    <t>Clause Type</t>
-  </si>
-  <si>
-    <t>Clause Description</t>
-  </si>
-  <si>
-    <t>Current Expiration Date</t>
-  </si>
-  <si>
-    <t>Days to Expiration</t>
-  </si>
-  <si>
-    <t>5.02 (iii)</t>
-  </si>
-  <si>
-    <t>5.03</t>
-  </si>
-  <si>
-    <t>7.03</t>
-  </si>
-  <si>
-    <t>Informe de Auditoría Financiera Externa</t>
-  </si>
-  <si>
-    <t>5.02 y 7.03 (a)</t>
-  </si>
-  <si>
     <t>5823/OC-CR</t>
-  </si>
-  <si>
-    <t>Informes de Auditoría Financiera Externa</t>
-  </si>
-  <si>
-    <t>5.03 (a)</t>
-  </si>
-  <si>
-    <t>Informe de Evaluación Intermedia</t>
-  </si>
-  <si>
-    <t>5.01 (c) - I Semestre 2026</t>
-  </si>
-  <si>
-    <t>Informes Semestrales</t>
-  </si>
-  <si>
-    <t>5.01 (c) y 7.02</t>
-  </si>
-  <si>
-    <t>Informes Semestrales de Progreso</t>
   </si>
   <si>
     <t>Fecha de corte: 06 abril 2026</t>
@@ -1301,39 +1181,6 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>Estados Financieros Anuales Auditados del Programa</t>
-  </si>
-  <si>
-    <t>Estados Financieros Auditados anuales</t>
-  </si>
-  <si>
-    <t>Recibidos y en revisión</t>
-  </si>
-  <si>
-    <t>1.04</t>
-  </si>
-  <si>
-    <t>Plazo de último desembolso</t>
-  </si>
-  <si>
-    <t>4.07</t>
-  </si>
-  <si>
-    <t>5777/GR-CR</t>
-  </si>
-  <si>
-    <t>Plan de mantenimiento e informe anual de mantenimiento</t>
-  </si>
-  <si>
-    <t>5,02</t>
-  </si>
-  <si>
-    <t>5.01</t>
-  </si>
-  <si>
-    <t>Sectorial Prior Condition</t>
-  </si>
-  <si>
     <t>OVIEDO BENAVIDES, GUSTAVO ALONSO</t>
   </si>
   <si>
@@ -1437,16 +1284,25 @@
   </si>
   <si>
     <t>agrega referencia a firma autorizada</t>
+  </si>
+  <si>
+    <t>se eliminan las hojas antiguas de clausulas en excel y se limpia para asegurar referencias al csv nuevo</t>
+  </si>
+  <si>
+    <t>Asigna como analista 1 al responsible del equipo de operaciones</t>
+  </si>
+  <si>
+    <t>pmr</t>
+  </si>
+  <si>
+    <t>actualiza codigo de colores para indicadores tecnicos segun guía de pmr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-10409]dd\-mmm\-yyyy"/>
-  </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1469,19 +1325,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1592,14 +1435,8 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1620,12 +1457,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF307899"/>
-        <bgColor rgb="FF307899"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1637,7 +1468,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1682,19 +1513,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD3D3D3"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD3D3D3"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD3D3D3"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1947,10 +1765,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1968,34 +1786,28 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2004,170 +1816,164 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2184,23 +1990,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2545,829 +2348,829 @@
   <dimension ref="A1:D60"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" style="66" customWidth="1"/>
-    <col min="2" max="2" width="38" style="66" customWidth="1"/>
-    <col min="3" max="3" width="42" style="66" customWidth="1"/>
-    <col min="4" max="4" width="80" style="66" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="66"/>
+    <col min="1" max="1" width="14" style="61" customWidth="1"/>
+    <col min="2" max="2" width="38" style="61" customWidth="1"/>
+    <col min="3" max="3" width="42" style="61" customWidth="1"/>
+    <col min="4" max="4" width="80" style="61" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="61"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
     </row>
     <row r="2" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="62" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="68" t="s">
+      <c r="C4" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="63" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="63" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="63" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="68" t="s">
+      <c r="D7" s="63" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="68" t="s">
+      <c r="C8" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="68" t="s">
+      <c r="D8" s="63" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="68" t="s">
+      <c r="D9" s="63" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="67" t="s">
+      <c r="A10" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="68" t="s">
+      <c r="B10" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="68" t="s">
+      <c r="D10" s="63" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="67" t="s">
+      <c r="A11" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="68" t="s">
+      <c r="B11" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="68" t="s">
+      <c r="C11" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="68" t="s">
+      <c r="D11" s="63" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="63" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="68" t="s">
+      <c r="D13" s="63" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="67" t="s">
+      <c r="A14" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="68" t="s">
+      <c r="B14" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="68" t="s">
+      <c r="D14" s="63" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="67" t="s">
+      <c r="A15" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="68" t="s">
+      <c r="B15" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="68" t="s">
+      <c r="D15" s="63" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="67" t="s">
+      <c r="A16" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="68" t="s">
+      <c r="B16" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="68" t="s">
+      <c r="D16" s="63" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="67" t="s">
+      <c r="A17" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="68" t="s">
+      <c r="D17" s="63" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="68" t="s">
+      <c r="B18" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="68"/>
+      <c r="D18" s="63"/>
     </row>
     <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="68" t="s">
+      <c r="B19" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="68" t="s">
+      <c r="D19" s="63" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="67" t="s">
+      <c r="A20" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="68" t="s">
+      <c r="D20" s="63" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="67" t="s">
+      <c r="A21" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="68" t="s">
+      <c r="B21" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="68" t="s">
+      <c r="D21" s="63" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="67" t="s">
+      <c r="A22" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="68" t="s">
+      <c r="D22" s="63" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="68" t="s">
+      <c r="B23" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="68" t="s">
+      <c r="D23" s="63" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="68" t="s">
+      <c r="B24" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="68" t="s">
+      <c r="D24" s="63" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="67" t="s">
+      <c r="A25" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="68" t="s">
+      <c r="C25" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="68" t="s">
+      <c r="D25" s="63" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="67" t="s">
+      <c r="A26" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="68" t="s">
+      <c r="B26" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="68" t="s">
+      <c r="D26" s="63" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="67" t="s">
+      <c r="A27" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="68" t="s">
+      <c r="D27" s="63" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="67" t="s">
+      <c r="A28" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="68" t="s">
+      <c r="B28" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="68" t="s">
+      <c r="D28" s="63" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="67" t="s">
+      <c r="A29" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="68" t="s">
+      <c r="B29" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="68" t="s">
+      <c r="D29" s="63" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="67" t="s">
+      <c r="A30" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="68" t="s">
+      <c r="B30" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="68" t="s">
+      <c r="D30" s="63" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="67" t="s">
+      <c r="A31" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="68" t="s">
+      <c r="B31" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="D31" s="68" t="s">
+      <c r="D31" s="63" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="67" t="s">
+      <c r="A32" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="68" t="s">
+      <c r="B32" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="68" t="s">
+      <c r="D32" s="63" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="67" t="s">
+      <c r="A33" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="68" t="s">
+      <c r="B33" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="68" t="s">
+      <c r="C33" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="68" t="s">
+      <c r="D33" s="63" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="67" t="s">
+      <c r="A34" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="68" t="s">
+      <c r="B34" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="D34" s="68" t="s">
+      <c r="D34" s="63" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="67" t="s">
+      <c r="A35" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="68" t="s">
+      <c r="B35" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="68" t="s">
+      <c r="D35" s="63" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="67" t="s">
+      <c r="A36" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="68" t="s">
+      <c r="B36" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="D36" s="68" t="s">
+      <c r="D36" s="63" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="67" t="s">
+      <c r="A37" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="68" t="s">
+      <c r="B37" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="68" t="s">
+      <c r="C37" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="D37" s="68" t="s">
+      <c r="D37" s="63" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="67" t="s">
+      <c r="A38" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="68" t="s">
+      <c r="B38" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="68" t="s">
+      <c r="C38" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="68" t="s">
+      <c r="D38" s="63" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="67" t="s">
+      <c r="A39" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="68" t="s">
+      <c r="B39" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="68" t="s">
+      <c r="D39" s="63" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="67" t="s">
+      <c r="A40" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="68" t="s">
+      <c r="B40" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="68" t="s">
+      <c r="C40" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="68" t="s">
+      <c r="D40" s="63" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="67" t="s">
+      <c r="A41" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="68" t="s">
+      <c r="B41" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="68" t="s">
+      <c r="C41" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="68" t="s">
+      <c r="D41" s="63" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="67" t="s">
+      <c r="A42" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="68" t="s">
+      <c r="B42" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C42" s="68" t="s">
+      <c r="C42" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="D42" s="68" t="s">
+      <c r="D42" s="63" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="67" t="s">
+      <c r="A43" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="68" t="s">
+      <c r="B43" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="68" t="s">
+      <c r="C43" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="D43" s="68" t="s">
+      <c r="D43" s="63" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="67" t="s">
+      <c r="A44" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B44" s="68" t="s">
+      <c r="B44" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="68" t="s">
+      <c r="C44" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="68" t="s">
+      <c r="D44" s="63" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="67" t="s">
+      <c r="A45" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="68" t="s">
+      <c r="B45" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="D45" s="68" t="s">
+      <c r="D45" s="63" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="67" t="s">
+      <c r="A46" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B46" s="68" t="s">
+      <c r="B46" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="68" t="s">
+      <c r="C46" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="68" t="s">
+      <c r="D46" s="63" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="67" t="s">
+      <c r="A47" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="68" t="s">
+      <c r="B47" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="68" t="s">
+      <c r="C47" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="68" t="s">
+      <c r="D47" s="63" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="67" t="s">
+      <c r="A48" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="68" t="s">
+      <c r="B48" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="68" t="s">
+      <c r="C48" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="D48" s="68" t="s">
+      <c r="D48" s="63" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="67" t="s">
+      <c r="A49" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="68" t="s">
+      <c r="B49" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="68" t="s">
+      <c r="C49" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="D49" s="68" t="s">
+      <c r="D49" s="63" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="67" t="s">
+      <c r="A50" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B50" s="68" t="s">
+      <c r="B50" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="68" t="s">
+      <c r="D50" s="63" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="67" t="s">
+      <c r="A51" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="68" t="s">
+      <c r="B51" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="68" t="s">
+      <c r="C51" s="63" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="68" t="s">
+      <c r="D51" s="63" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="67" t="s">
+      <c r="A52" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="68" t="s">
+      <c r="B52" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="68" t="s">
+      <c r="C52" s="63" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="68" t="s">
+      <c r="D52" s="63" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="67" t="s">
+      <c r="A53" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B53" s="68" t="s">
+      <c r="B53" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="D53" s="68" t="s">
+      <c r="D53" s="63" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="67" t="s">
+      <c r="A54" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B54" s="68" t="s">
+      <c r="B54" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="68" t="s">
+      <c r="C54" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="68" t="s">
+      <c r="D54" s="63" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="67" t="s">
+      <c r="A55" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B55" s="68" t="s">
+      <c r="B55" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="68" t="s">
+      <c r="C55" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="68" t="s">
+      <c r="D55" s="63" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="67" t="s">
+      <c r="A56" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B56" s="68" t="s">
+      <c r="B56" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="C56" s="68" t="s">
+      <c r="C56" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="D56" s="68" t="s">
-        <v>439</v>
+      <c r="D56" s="63" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="67" t="s">
+      <c r="A57" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="68" t="s">
+      <c r="B57" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="68" t="s">
+      <c r="C57" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="D57" s="68" t="s">
+      <c r="D57" s="63" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="67" t="s">
+      <c r="A58" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="68" t="s">
+      <c r="B58" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="C58" s="68" t="s">
+      <c r="C58" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="D58" s="68" t="s">
+      <c r="D58" s="63" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="67" t="s">
+      <c r="A59" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="68" t="s">
+      <c r="B59" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="68" t="s">
-        <v>438</v>
-      </c>
-      <c r="D59" s="68" t="s">
-        <v>437</v>
+      <c r="C59" s="63" t="s">
+        <v>388</v>
+      </c>
+      <c r="D59" s="63" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="67" t="s">
+      <c r="A60" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B60" s="68" t="s">
+      <c r="B60" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="C60" s="68" t="s">
+      <c r="C60" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="D60" s="68" t="s">
+      <c r="D60" s="63" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3640,16 +3443,16 @@
         <v>152</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>153</v>
@@ -3664,7 +3467,7 @@
         <v>153</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>411</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
@@ -3687,7 +3490,7 @@
         <v>157</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>414</v>
+        <v>364</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>157</v>
@@ -3725,17 +3528,17 @@
       <c r="B16" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>160</v>
+      <c r="C16" s="7" t="s">
+        <v>363</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>160</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>163</v>
@@ -3744,13 +3547,13 @@
         <v>161</v>
       </c>
       <c r="I16" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
@@ -3761,13 +3564,13 @@
         <v>161</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>161</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>161</v>
@@ -3776,13 +3579,13 @@
         <v>163</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>413</v>
+        <v>161</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
@@ -3793,24 +3596,23 @@
         <v>169</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>164</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="J18" s="5"/>
+        <v>363</v>
+      </c>
       <c r="K18" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
@@ -3818,21 +3620,20 @@
         <v>168</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
         <v>167</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>163</v>
+        <v>365</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
@@ -3851,21 +3652,19 @@
         <v>167</v>
       </c>
       <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>413</v>
+      <c r="C21" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
     </row>
@@ -3875,813 +3674,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:K14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="5" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="45.42578125" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="44.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="6">
-        <v>46160</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="9">
-        <v>670362</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="J5" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="9">
-        <v>664364</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="J6" s="11">
-        <v>46112</v>
-      </c>
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="9">
-        <v>705321</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="J7" s="11">
-        <v>46112</v>
-      </c>
-      <c r="K7" s="10"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="9">
-        <v>705320</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="J8" s="11">
-        <v>46112</v>
-      </c>
-      <c r="K8" s="10"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="9">
-        <v>690057</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="J9" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="9">
-        <v>690057</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="J10" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="9">
-        <v>701800</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="J11" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="9">
-        <v>692690</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="J12" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="B13" s="9">
-        <v>701558</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="J13" s="11">
-        <v>46112</v>
-      </c>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="9">
-        <v>687164</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="J14" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>402</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="22" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:K15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="6">
-        <v>46160</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="10">
-        <v>692694</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="J5" s="11">
-        <v>46214</v>
-      </c>
-      <c r="K5" s="10">
-        <f t="shared" ref="K5:K13" ca="1" si="0">J5-TODAY()</f>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="10">
-        <v>701797</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="J6" s="11">
-        <v>46249</v>
-      </c>
-      <c r="K6" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="10">
-        <v>691923</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="J7" s="11">
-        <v>46265</v>
-      </c>
-      <c r="K7" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="10">
-        <v>691920</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="J8" s="11">
-        <v>46265</v>
-      </c>
-      <c r="K8" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="10">
-        <v>692683</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="J9" s="11">
-        <v>46280</v>
-      </c>
-      <c r="K9" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="10">
-        <v>701675</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="J10" s="11">
-        <v>46282</v>
-      </c>
-      <c r="K10" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="B11" s="10">
-        <v>664339</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="J11" s="11">
-        <v>46282</v>
-      </c>
-      <c r="K11" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="10">
-        <v>191156</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="J12" s="11">
-        <v>46339</v>
-      </c>
-      <c r="K12" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>169</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="10">
-        <v>191155</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="J13" s="11">
-        <v>46339</v>
-      </c>
-      <c r="K13" s="10">
-        <f t="shared" ca="1" si="0"/>
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="24" x14ac:dyDescent="0.25">
-      <c r="B14" s="10">
-        <v>701540</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="J14" s="11">
-        <v>46266</v>
-      </c>
-      <c r="K14" s="10">
-        <f t="shared" ref="K14:K15" ca="1" si="1">J14-TODAY()</f>
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="10">
-        <v>701557</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="J15" s="11">
-        <v>46326</v>
-      </c>
-      <c r="K15" s="10">
-        <f t="shared" ca="1" si="1"/>
-        <v>156</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="B4:K13" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:K13">
-      <sortCondition ref="K4:K13"/>
-    </sortState>
-  </autoFilter>
-  <phoneticPr fontId="22" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:G41"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4698,701 +3690,701 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="38" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="26" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="31" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="F14" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="28" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="14" t="s">
+      <c r="D17" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="E17" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="F17" s="30"/>
+      <c r="G17" s="31" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D18" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="F18" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="G18" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="F3" s="15" t="s">
+    </row>
+    <row r="19" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="D20" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="F20" s="18" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="G20" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="D4" s="19" t="s">
+    </row>
+    <row r="21" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="E22" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="21" t="s">
+      <c r="F22" s="25"/>
+      <c r="G22" s="72"/>
+    </row>
+    <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" s="18"/>
+      <c r="G23" s="74"/>
+    </row>
+    <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="G24" s="74"/>
+    </row>
+    <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E25" s="18"/>
+      <c r="G25" s="74"/>
+    </row>
+    <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E26" s="18"/>
+      <c r="G26" s="74"/>
+    </row>
+    <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="G27" s="74"/>
+    </row>
+    <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="G28" s="74"/>
+    </row>
+    <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="75" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="76" t="s">
+        <v>366</v>
+      </c>
+      <c r="D29" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="E29" s="78" t="s">
+        <v>367</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="G29" s="79" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="23" t="s">
+    <row r="30" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D30" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G5" s="25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="23" t="s">
+      <c r="F30" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="G30" s="20" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F31" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="G6" s="25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="G31" s="20" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="D32" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="F7" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="28" t="s">
+      <c r="F32" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31" t="s">
+      <c r="G32" s="20" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="18" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="9" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="D33" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="F33" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E10" s="23" t="s">
+      <c r="G33" s="39" t="s">
         <v>239</v>
       </c>
-      <c r="F10" s="23" t="s">
-        <v>433</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="58.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="33" t="s">
+    </row>
+    <row r="34" spans="2:7" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="D11" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="36" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="18" t="s">
+      <c r="C34" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="E12" s="18" t="s">
+      <c r="D34" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F34" s="82" t="s">
         <v>243</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G34" s="16" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="33" t="s">
+    <row r="35" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="C35" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="D13" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="E13" s="33" t="s">
+      <c r="D35" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E35" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="F13" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="G13" s="36" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="39" t="s">
+      <c r="F35" s="83"/>
+      <c r="G35" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="D14" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="E14" s="39" t="s">
+    </row>
+    <row r="36" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="E36" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F36" s="83"/>
+      <c r="G36" s="20" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="G14" s="42" t="s">
+      <c r="D37" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="18" t="s">
+      <c r="F37" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="E15" s="18" t="s">
+      <c r="G37" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="F15" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="G15" s="21" t="s">
+    </row>
+    <row r="38" spans="2:7" ht="188.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="D38" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E16" s="23" t="s">
+      <c r="F38" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="G38" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="G16" s="25" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="33" t="s">
+    </row>
+    <row r="39" spans="2:7" ht="193.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D17" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="E17" s="33" t="s">
+      <c r="D39" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="20" t="s">
+      <c r="F39" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="D18" s="37" t="s">
-        <v>428</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="F18" s="18" t="s">
+      <c r="G39" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="G18" s="21" t="s">
+    </row>
+    <row r="40" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>428</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="F19" s="23"/>
-      <c r="G19" s="25"/>
-    </row>
-    <row r="20" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D40" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="G40" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="D20" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="F20" s="23" t="s">
+    </row>
+    <row r="41" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="D41" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="E41" s="30"/>
+      <c r="F41" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="G41" s="31" t="s">
         <v>263</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>432</v>
-      </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-    </row>
-    <row r="22" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="76" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="D22" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="F22" s="30"/>
-      <c r="G22" s="77"/>
-    </row>
-    <row r="23" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E23" s="23"/>
-      <c r="G23" s="79"/>
-    </row>
-    <row r="24" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E24" s="23"/>
-      <c r="G24" s="79"/>
-    </row>
-    <row r="25" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E25" s="23"/>
-      <c r="G25" s="79"/>
-    </row>
-    <row r="26" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E26" s="23"/>
-      <c r="G26" s="79"/>
-    </row>
-    <row r="27" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E27" s="23"/>
-      <c r="G27" s="79"/>
-    </row>
-    <row r="28" spans="2:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>419</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>426</v>
-      </c>
-      <c r="G28" s="79"/>
-    </row>
-    <row r="29" spans="2:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="80" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="81" t="s">
-        <v>416</v>
-      </c>
-      <c r="D29" s="82" t="s">
-        <v>228</v>
-      </c>
-      <c r="E29" s="83" t="s">
-        <v>417</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>426</v>
-      </c>
-      <c r="G29" s="84" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="G30" s="25" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="G31" s="25" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="G32" s="25" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G33" s="44" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="F34" s="87" t="s">
-        <v>282</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="D35" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>285</v>
-      </c>
-      <c r="F35" s="88"/>
-      <c r="G35" s="25" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="F36" s="88"/>
-      <c r="G36" s="25" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" ht="195" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="F37" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="G37" s="21" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" ht="188.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="G38" s="25" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" ht="193.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="G39" s="25" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D40" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="G40" s="25" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="D41" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="E41" s="35"/>
-      <c r="F41" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="G41" s="36" t="s">
-        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -5404,7 +4396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:Q14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5424,421 +4416,421 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="65" t="s">
-        <v>303</v>
-      </c>
-      <c r="C2" s="65"/>
+      <c r="B2" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="60"/>
     </row>
     <row r="4" spans="2:17" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="74" t="s">
-        <v>174</v>
-      </c>
-      <c r="C4" s="74" t="s">
-        <v>399</v>
-      </c>
-      <c r="D4" s="73" t="s">
-        <v>387</v>
-      </c>
-      <c r="E4" s="63" t="s">
-        <v>388</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>304</v>
-      </c>
-      <c r="G4" s="64" t="s">
-        <v>305</v>
-      </c>
-      <c r="H4" s="64" t="s">
-        <v>306</v>
-      </c>
-      <c r="I4" s="64" t="s">
-        <v>307</v>
-      </c>
-      <c r="J4" s="64" t="s">
-        <v>308</v>
-      </c>
-      <c r="K4" s="64" t="s">
-        <v>309</v>
-      </c>
-      <c r="L4" s="64" t="s">
-        <v>310</v>
-      </c>
-      <c r="M4" s="63" t="s">
-        <v>311</v>
-      </c>
-      <c r="N4" s="63" t="s">
-        <v>312</v>
+      <c r="B4" s="69" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>348</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>349</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>265</v>
+      </c>
+      <c r="G4" s="59" t="s">
+        <v>266</v>
+      </c>
+      <c r="H4" s="59" t="s">
+        <v>267</v>
+      </c>
+      <c r="I4" s="59" t="s">
+        <v>268</v>
+      </c>
+      <c r="J4" s="59" t="s">
+        <v>269</v>
+      </c>
+      <c r="K4" s="59" t="s">
+        <v>270</v>
+      </c>
+      <c r="L4" s="59" t="s">
+        <v>271</v>
+      </c>
+      <c r="M4" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="N4" s="58" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="75" t="s">
-        <v>389</v>
-      </c>
-      <c r="D5" s="69" t="s">
-        <v>313</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>313</v>
-      </c>
-      <c r="F5" s="50">
+      <c r="C5" s="70" t="s">
+        <v>350</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="F5" s="45">
         <v>0.77</v>
       </c>
-      <c r="G5" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="H5" s="52">
+      <c r="G5" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="H5" s="47">
         <v>1</v>
       </c>
-      <c r="I5" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="J5" s="52">
+      <c r="I5" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="J5" s="47">
         <v>1.01</v>
       </c>
-      <c r="K5" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="L5" s="47">
+      <c r="K5" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="L5" s="42">
         <v>2</v>
       </c>
-      <c r="M5" s="45" t="s">
-        <v>315</v>
-      </c>
-      <c r="N5" s="45" t="s">
-        <v>316</v>
+      <c r="M5" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="N5" s="40" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="75" t="s">
-        <v>390</v>
-      </c>
-      <c r="D6" s="70" t="s">
-        <v>317</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F6" s="54">
+      <c r="C6" s="70" t="s">
+        <v>351</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F6" s="49">
         <v>0.97</v>
       </c>
-      <c r="G6" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="H6" s="52">
+      <c r="G6" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="H6" s="47">
         <v>0.95</v>
       </c>
-      <c r="I6" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="J6" s="52">
+      <c r="I6" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="J6" s="47">
         <v>1.05</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="48">
         <v>6</v>
       </c>
-      <c r="L6" s="47">
+      <c r="L6" s="42">
         <v>3</v>
       </c>
-      <c r="M6" s="45" t="s">
-        <v>318</v>
-      </c>
-      <c r="N6" s="45" t="s">
-        <v>314</v>
+      <c r="M6" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="N6" s="40" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="75" t="s">
-        <v>391</v>
-      </c>
-      <c r="D7" s="70" t="s">
-        <v>317</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F7" s="54">
+      <c r="C7" s="70" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F7" s="49">
         <v>0.65000000000000191</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="50">
         <v>0.55202837426136353</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="47">
         <v>0.98070203221697061</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="47">
         <v>0.99829990031034122</v>
       </c>
-      <c r="J7" s="52">
+      <c r="J7" s="47">
         <v>1.0760758704453901</v>
       </c>
-      <c r="K7" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="L7" s="47">
+      <c r="K7" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="L7" s="42">
         <v>2</v>
       </c>
-      <c r="M7" s="45" t="s">
-        <v>319</v>
-      </c>
-      <c r="N7" s="45" t="s">
-        <v>320</v>
+      <c r="M7" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="N7" s="40" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="75" t="s">
-        <v>392</v>
-      </c>
-      <c r="D8" s="70" t="s">
-        <v>317</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F8" s="56">
+      <c r="C8" s="70" t="s">
+        <v>353</v>
+      </c>
+      <c r="D8" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F8" s="51">
         <v>0.04</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8" s="47">
         <v>1.39</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8" s="47">
         <v>1.39</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8" s="47">
         <v>1</v>
       </c>
-      <c r="J8" s="52">
+      <c r="J8" s="47">
         <v>1</v>
       </c>
-      <c r="K8" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="L8" s="47">
+      <c r="K8" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="L8" s="42">
         <v>2</v>
       </c>
-      <c r="M8" s="45" t="s">
-        <v>321</v>
-      </c>
-      <c r="N8" s="45" t="s">
-        <v>322</v>
+      <c r="M8" s="40" t="s">
+        <v>282</v>
+      </c>
+      <c r="N8" s="40" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="75" t="s">
-        <v>393</v>
-      </c>
-      <c r="D9" s="69" t="s">
-        <v>313</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F9" s="54">
+      <c r="C9" s="70" t="s">
+        <v>354</v>
+      </c>
+      <c r="D9" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F9" s="49">
         <v>0.65</v>
       </c>
-      <c r="G9" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="H9" s="55">
+      <c r="G9" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="H9" s="50">
         <v>0.75</v>
       </c>
-      <c r="I9" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="J9" s="55">
+      <c r="I9" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="J9" s="50">
         <v>0.74</v>
       </c>
-      <c r="K9" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="L9" s="47">
+      <c r="K9" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="L9" s="42">
         <v>2</v>
       </c>
-      <c r="M9" s="45" t="s">
-        <v>323</v>
-      </c>
-      <c r="N9" s="45" t="s">
-        <v>324</v>
+      <c r="M9" s="40" t="s">
+        <v>284</v>
+      </c>
+      <c r="N9" s="40" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="75" t="s">
-        <v>394</v>
-      </c>
-      <c r="D10" s="71" t="s">
-        <v>325</v>
-      </c>
-      <c r="E10" s="58" t="s">
-        <v>325</v>
-      </c>
-      <c r="F10" s="54">
+      <c r="C10" s="70" t="s">
+        <v>355</v>
+      </c>
+      <c r="D10" s="66" t="s">
+        <v>286</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="F10" s="49">
         <v>0.38000000000000012</v>
       </c>
-      <c r="G10" s="57">
+      <c r="G10" s="52">
         <v>3.2321905146600778E-2</v>
       </c>
-      <c r="H10" s="55">
+      <c r="H10" s="50">
         <v>0.4608036086469921</v>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="47">
         <v>1.129574230040155</v>
       </c>
-      <c r="J10" s="55">
+      <c r="J10" s="50">
         <v>2.737091349830477</v>
       </c>
-      <c r="K10" s="49" t="s">
-        <v>314</v>
-      </c>
-      <c r="L10" s="47">
+      <c r="K10" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="L10" s="42">
         <v>2</v>
       </c>
-      <c r="M10" s="45" t="s">
-        <v>326</v>
-      </c>
-      <c r="N10" s="45" t="s">
-        <v>327</v>
+      <c r="M10" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="N10" s="40" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="75" t="s">
-        <v>395</v>
-      </c>
-      <c r="D11" s="70" t="s">
-        <v>317</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F11" s="59">
+      <c r="C11" s="70" t="s">
+        <v>356</v>
+      </c>
+      <c r="D11" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F11" s="54">
         <v>1</v>
       </c>
-      <c r="G11" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="H11" s="52">
+      <c r="G11" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="H11" s="47">
         <v>0.95</v>
       </c>
-      <c r="I11" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="J11" s="52">
+      <c r="I11" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="J11" s="47">
         <v>0.9</v>
       </c>
-      <c r="K11" s="47">
+      <c r="K11" s="42">
         <v>3</v>
       </c>
-      <c r="L11" s="47">
+      <c r="L11" s="42">
         <v>3</v>
       </c>
-      <c r="M11" s="45" t="s">
-        <v>318</v>
-      </c>
-      <c r="N11" s="45" t="s">
-        <v>314</v>
+      <c r="M11" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="N11" s="40" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="75" t="s">
-        <v>396</v>
-      </c>
-      <c r="D12" s="69" t="s">
-        <v>313</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="60" t="s">
-        <v>328</v>
-      </c>
-      <c r="N12" s="45" t="s">
-        <v>329</v>
+      <c r="C12" s="70" t="s">
+        <v>357</v>
+      </c>
+      <c r="D12" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="55" t="s">
+        <v>289</v>
+      </c>
+      <c r="N12" s="40" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="75" t="s">
-        <v>330</v>
-      </c>
-      <c r="C13" s="75" t="s">
-        <v>397</v>
-      </c>
-      <c r="D13" s="72" t="s">
-        <v>331</v>
-      </c>
-      <c r="E13" s="61" t="s">
-        <v>331</v>
-      </c>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="N13" s="45" t="s">
-        <v>329</v>
+      <c r="B13" s="70" t="s">
+        <v>291</v>
+      </c>
+      <c r="C13" s="70" t="s">
+        <v>358</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>292</v>
+      </c>
+      <c r="E13" s="56" t="s">
+        <v>292</v>
+      </c>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="N13" s="40" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="75" t="s">
-        <v>398</v>
-      </c>
-      <c r="D14" s="70" t="s">
-        <v>317</v>
-      </c>
-      <c r="E14" s="48" t="s">
-        <v>317</v>
-      </c>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="60" t="s">
-        <v>333</v>
-      </c>
-      <c r="N14" s="45" t="s">
-        <v>334</v>
-      </c>
-      <c r="P14" s="62"/>
-      <c r="Q14" s="62"/>
+      <c r="C14" s="70" t="s">
+        <v>359</v>
+      </c>
+      <c r="D14" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="55" t="s">
+        <v>294</v>
+      </c>
+      <c r="N14" s="40" t="s">
+        <v>295</v>
+      </c>
+      <c r="P14" s="57"/>
+      <c r="Q14" s="57"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5846,7 +4838,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F546759E-1E7A-4FBA-BCE7-8747DD03CB19}">
   <dimension ref="B2:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5856,13 +4848,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="D2" t="s">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="E2" t="s">
-        <v>389</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
@@ -5870,13 +4862,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="D3" t="s">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="E3" t="s">
-        <v>389</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
@@ -5884,10 +4876,10 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="E4" t="s">
-        <v>390</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
@@ -5895,13 +4887,13 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="D5" t="s">
-        <v>379</v>
+        <v>340</v>
       </c>
       <c r="E5" t="s">
-        <v>391</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
@@ -5909,13 +4901,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>380</v>
+        <v>341</v>
       </c>
       <c r="E6" t="s">
-        <v>392</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
@@ -5923,13 +4915,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
-        <v>381</v>
+        <v>342</v>
       </c>
       <c r="E7" t="s">
-        <v>393</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -5937,10 +4929,10 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>382</v>
+        <v>343</v>
       </c>
       <c r="E8" t="s">
-        <v>394</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
@@ -5948,10 +4940,10 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>383</v>
+        <v>344</v>
       </c>
       <c r="E9" t="s">
-        <v>395</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
@@ -5959,21 +4951,21 @@
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>384</v>
+        <v>345</v>
       </c>
       <c r="E10" t="s">
-        <v>396</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>330</v>
+        <v>291</v>
       </c>
       <c r="D11" t="s">
-        <v>386</v>
+        <v>347</v>
       </c>
       <c r="E11" t="s">
-        <v>397</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
@@ -5981,10 +4973,10 @@
         <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>385</v>
+        <v>346</v>
       </c>
       <c r="E12" t="s">
-        <v>398</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -5992,9 +4984,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:E40"/>
+  <dimension ref="B2:E43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -6006,524 +4998,557 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>335</v>
+        <v>296</v>
       </c>
       <c r="C2" t="s">
-        <v>336</v>
+        <v>297</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>337</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C3" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>340</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C4" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>341</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C5" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>342</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C6" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>343</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C7" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>344</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C8" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>345</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C9" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D9" t="s">
         <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>347</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C10" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>348</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C11" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D11" t="s">
         <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>349</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C12" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>350</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C13" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D13" t="s">
-        <v>351</v>
+        <v>312</v>
       </c>
       <c r="E13" t="s">
-        <v>350</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C14" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>352</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C15" t="s">
-        <v>353</v>
+        <v>314</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>354</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C16" t="s">
-        <v>353</v>
+        <v>314</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>355</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C17" t="s">
-        <v>353</v>
+        <v>314</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>356</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C18" t="s">
-        <v>357</v>
+        <v>318</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="13">
+      <c r="B19" s="8">
         <v>46092</v>
       </c>
       <c r="C19" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="13">
+      <c r="B20" s="8">
         <v>46092</v>
       </c>
       <c r="C20" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D20" t="s">
-        <v>351</v>
+        <v>312</v>
       </c>
       <c r="E20" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="13">
+      <c r="B21" s="8">
         <v>46092</v>
       </c>
       <c r="C21" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="13">
+      <c r="B22" s="8">
         <v>46092</v>
       </c>
       <c r="C22" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>360</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="13">
+      <c r="B23" s="8">
         <v>46092</v>
       </c>
       <c r="C23" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>360</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="13">
+      <c r="B24" s="8">
         <v>46092</v>
       </c>
       <c r="C24" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D24" t="s">
         <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>340</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="13">
+      <c r="B25" s="8">
         <v>46092</v>
       </c>
       <c r="C25" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D25" t="s">
         <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>361</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26" s="13">
+      <c r="B26" s="8">
         <v>46119</v>
       </c>
       <c r="C26" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="E26" t="s">
-        <v>362</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="13">
+      <c r="B27" s="8">
         <v>46119</v>
       </c>
       <c r="C27" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>363</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="13">
+      <c r="B28" s="8">
         <v>46119</v>
       </c>
       <c r="C28" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>364</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="13">
+      <c r="B29" s="8">
         <v>46119</v>
       </c>
       <c r="C29" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="D29" t="s">
         <v>22</v>
       </c>
       <c r="E29" t="s">
-        <v>364</v>
+        <v>325</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="13">
+      <c r="B30" s="8">
         <v>46121</v>
       </c>
       <c r="C30" t="s">
-        <v>365</v>
+        <v>326</v>
       </c>
       <c r="D30" t="s">
-        <v>366</v>
+        <v>327</v>
       </c>
       <c r="E30" t="s">
-        <v>367</v>
+        <v>328</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="13">
+      <c r="B31" s="8">
         <v>46121</v>
       </c>
       <c r="C31" t="s">
-        <v>368</v>
+        <v>329</v>
       </c>
       <c r="D31" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
       <c r="E31" t="s">
-        <v>370</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B32" s="13">
+      <c r="B32" s="8">
         <v>46126</v>
       </c>
       <c r="C32" t="s">
-        <v>371</v>
+        <v>332</v>
       </c>
       <c r="D32" t="s">
-        <v>372</v>
+        <v>333</v>
       </c>
       <c r="E32" t="s">
-        <v>373</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="13">
+      <c r="B33" s="8">
         <v>46134</v>
       </c>
       <c r="C33" t="s">
-        <v>374</v>
+        <v>335</v>
       </c>
       <c r="E33" t="s">
-        <v>375</v>
+        <v>336</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="13">
+      <c r="B34" s="8">
         <v>46134</v>
       </c>
       <c r="C34" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="E34" t="s">
-        <v>376</v>
+        <v>337</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="13">
+      <c r="B35" s="8">
         <v>46142</v>
       </c>
       <c r="C35" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="E35" t="s">
-        <v>440</v>
+        <v>390</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B36" s="13">
+      <c r="B36" s="8">
         <v>46160</v>
       </c>
       <c r="C36" t="s">
-        <v>346</v>
+        <v>307</v>
       </c>
       <c r="E36" t="s">
-        <v>441</v>
+        <v>391</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="13">
+      <c r="B37" s="8">
         <v>46169</v>
       </c>
       <c r="C37" t="s">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="E37" t="s">
-        <v>436</v>
+        <v>386</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="13">
+      <c r="B38" s="8">
         <v>46170</v>
       </c>
       <c r="C38" t="s">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="E38" t="s">
-        <v>442</v>
+        <v>392</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="13">
+      <c r="B39" s="8">
         <v>46170</v>
       </c>
       <c r="C39" t="s">
-        <v>443</v>
+        <v>393</v>
       </c>
       <c r="E39" t="s">
-        <v>444</v>
+        <v>394</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B40" s="13">
+      <c r="B40" s="8">
         <v>46170</v>
       </c>
       <c r="C40" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="D40" t="s">
         <v>58</v>
       </c>
       <c r="E40" t="s">
-        <v>445</v>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B41" s="8">
+        <v>46171</v>
+      </c>
+      <c r="C41" t="s">
+        <v>385</v>
+      </c>
+      <c r="E41" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B42" s="8">
+        <v>46171</v>
+      </c>
+      <c r="C42" t="s">
+        <v>307</v>
+      </c>
+      <c r="E42" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B43" s="8">
+        <v>46171</v>
+      </c>
+      <c r="C43" t="s">
+        <v>398</v>
+      </c>
+      <c r="E43" t="s">
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -6532,6 +5557,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6eb7e908-d61c-4846-9ec9-1ad75cf16705" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4ddaf961-75a3-44f9-b9a0-6c4032ed836e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090862990C7B69B4FACED7B33CDEA6B2D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cb2feda0469996778cb97eaa0df7bf34">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4ddaf961-75a3-44f9-b9a0-6c4032ed836e" xmlns:ns3="6eb7e908-d61c-4846-9ec9-1ad75cf16705" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ee5c23c3434d1001a3ba2f51c828df17" ns2:_="" ns3:_="">
     <xsd:import namespace="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
@@ -6772,17 +5808,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6eb7e908-d61c-4846-9ec9-1ad75cf16705" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4ddaf961-75a3-44f9-b9a0-6c4032ed836e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6793,6 +5818,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6eb7e908-d61c-4846-9ec9-1ad75cf16705"/>
+    <ds:schemaRef ds:uri="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186B4DCA-A60A-452A-99AD-03FF95333E10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6811,17 +5847,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1C5BB8-2969-4B26-83EB-3E0EFA4C2B46}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6eb7e908-d61c-4846-9ec9-1ad75cf16705"/>
-    <ds:schemaRef ds:uri="4ddaf961-75a3-44f9-b9a0-6c4032ed836e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F155E963-344D-4195-BD2C-0A3B31EF9B00}">
   <ds:schemaRefs>
